--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z\Desktop\robot\zgps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z\Desktop\robot\开源\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44204C1B-BEAC-4EE7-B1D9-DE458375D768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0377594-6D09-4139-8ADB-20D365E462A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>物料编号</t>
   </si>
@@ -62,9 +62,6 @@
     <t>串行舵机连接线 30cm</t>
   </si>
   <si>
-    <t>南古 T62-L舵机</t>
-  </si>
-  <si>
     <t>microzone MC6C遥控器+接收器+电池</t>
   </si>
   <si>
@@ -198,13 +195,21 @@
   </si>
   <si>
     <t>三绿ABS耗材1KG</t>
+  </si>
+  <si>
+    <t>星辉S80 180°舵机</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>大扭矩带堵转保护舵机</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +237,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -270,6 +283,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,6 +587,7 @@
   <cols>
     <col min="2" max="2" width="52.1640625" customWidth="1"/>
     <col min="6" max="6" width="49.25" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -648,17 +665,20 @@
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>105</v>
+        <v>288</v>
       </c>
       <c r="E5" s="4">
-        <v>105</v>
+        <v>288</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -666,7 +686,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -683,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4">
         <v>200</v>
@@ -693,7 +713,7 @@
         <v>13.9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -701,7 +721,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4">
         <v>300</v>
@@ -716,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4">
         <v>50</v>
@@ -731,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4">
         <v>50</v>
@@ -746,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4">
         <v>50</v>
@@ -761,7 +781,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4">
         <v>200</v>
@@ -776,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="4">
         <v>100</v>
@@ -791,7 +811,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="4">
         <v>50</v>
@@ -806,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4">
         <v>50</v>
@@ -821,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4">
         <v>20</v>
@@ -836,7 +856,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4">
         <v>40</v>
@@ -851,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="4">
         <v>20</v>
@@ -866,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4">
         <v>20</v>
@@ -881,7 +901,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4">
         <v>100</v>
@@ -896,7 +916,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4">
         <v>30</v>
@@ -913,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4">
         <v>30</v>
@@ -930,7 +950,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="4">
         <v>6</v>
@@ -947,7 +967,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="4">
         <v>24</v>
@@ -964,7 +984,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
@@ -976,7 +996,7 @@
         <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -984,7 +1004,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="4">
         <v>50</v>
@@ -996,7 +1016,7 @@
         <v>13.2</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1004,7 +1024,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="4">
         <v>200</v>
@@ -1021,7 +1041,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="4">
         <v>20</v>
@@ -1038,7 +1058,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="4">
         <v>10</v>
@@ -1055,7 +1075,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="4">
         <v>20</v>
@@ -1072,7 +1092,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4">
         <v>20</v>
@@ -1089,7 +1109,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="4">
         <v>1</v>
@@ -1106,7 +1126,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
@@ -1118,7 +1138,7 @@
         <v>29</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1126,7 +1146,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
@@ -1143,7 +1163,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" s="4">
         <v>1</v>
@@ -1160,7 +1180,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -1177,7 +1197,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="4">
         <v>1</v>
@@ -1187,7 +1207,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1195,7 +1215,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
@@ -1207,7 +1227,7 @@
         <v>28.5</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1215,7 +1235,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="4">
         <v>12</v>
@@ -1232,7 +1252,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="4">
         <v>6</v>
@@ -1249,7 +1269,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="4">
         <v>6</v>
@@ -1266,7 +1286,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="4">
         <v>12</v>
@@ -1283,7 +1303,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="4">
         <v>12</v>
@@ -1300,7 +1320,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" s="4">
         <v>3</v>
@@ -1315,7 +1335,7 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E45">
         <f>SUM(E2:E44)</f>
-        <v>3177.0600000000004</v>
+        <v>3360.0600000000004</v>
       </c>
     </row>
   </sheetData>
